--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N89_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N89_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>83.1813543933378</v>
+        <v>13.51697008891739</v>
       </c>
       <c r="D2" t="n">
-        <v>39.15283443691458</v>
+        <v>6.36233559599862</v>
       </c>
       <c r="E2" t="n">
-        <v>11.23630300240227</v>
+        <v>1.82589923789037</v>
       </c>
       <c r="F2" t="n">
-        <v>11.93943986049775</v>
+        <v>1.940158977330885</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>71.82902402596916</v>
+        <v>11.67221640421999</v>
       </c>
       <c r="D3" t="n">
-        <v>24.15286962476946</v>
+        <v>3.924841314025037</v>
       </c>
       <c r="E3" t="n">
-        <v>11.23630300240227</v>
+        <v>1.82589923789037</v>
       </c>
       <c r="F3" t="n">
-        <v>11.93943986049775</v>
+        <v>1.940158977330885</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.79139820829528</v>
+        <v>9.066102208847983</v>
       </c>
       <c r="D4" t="n">
-        <v>53.39513343245206</v>
+        <v>8.676709182773459</v>
       </c>
       <c r="E4" t="n">
-        <v>11.23630300240227</v>
+        <v>1.82589923789037</v>
       </c>
       <c r="F4" t="n">
-        <v>11.93943986049775</v>
+        <v>1.940158977330885</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
